--- a/data/eval/hist_spot_check.xlsx
+++ b/data/eval/hist_spot_check.xlsx
@@ -433,10 +433,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,35 +449,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1. 在“逐条核对”表里，每一行是系统从一份公告里抽出的一条记录；点“公告链接”打开原文 PDF，翻到“页码”那一页。</t>
+          <t>目的：检查系统从公告里抽出的数字和名称对不对、有没有漏。标准答案只有一个：公告原文。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2. 对“对方 / 金额 / 单位 / 页码 / 上年实际”逐项选：对、错（错的话在备注写正确值）、原文没有。</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3. 在“漏抽统计”表里，写下这份公告里还有多少条同类记录系统没有抽出来（只数关联交易表或担保明细里的行）。</t>
+          <t>一、逐条核对（表“逐条核对”，62 行）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4. 每份公告只列了系统抽出的前 5 条；核对这 5 条即可，漏抽只数整份公告。</t>
+          <t>1. 点“公告链接”打开原文 PDF，翻到“页码”那一页（页码按 PDF 第几页算，不是印在页脚的页码）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5. 拿不准的写进备注，不要猜。做完把文件发回即可。</t>
+          <t>2. 在那一页的表格里找到“对方”这一行，然后逐项判断，在黄色格子里选：对 / 错 / 原文没有。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   对方对吗：公司名称与原文一致即为对（简称与全称指同一家公司也算对）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   金额对吗：关联交易看“预计金额（本年度预计）”那一列；担保看“担保额度 / 担保金额”。数字完全相同为对，千分位逗号不算差别。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   单位对吗：看表头或表格上方写的单位（元 / 万元 / 亿元），与“单位”列一致为对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   页码对吗：这条记录确实在该页为对；在别的页为错，在备注写正确页码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   上年实际对吗（只有关联交易有）：看“上年实际发生金额”那一列。注意有的表有三列数字（本年预计、本年截至披露日已发生、上年实际），要看表头选对列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3. 选“错”时，在备注写原文的正确值，例如“原文为 632,065.26”。原文里根本找不到这条记录时，各项都选“原文没有”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>二、漏抽统计（表“漏抽统计”，20 行）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4. 每份公告数一下原文主表（关联交易预计表或担保明细表）里一共有多少条记录，填在“原文表格中的记录条数”。不数“合计”“小计”行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   系统抽出的条数已经写在旁边；两者的差就是漏抽（或多抽），由我们来算，你只需要数原文。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>三、交回</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5. 拿不准的写进备注，不要猜。全部填完把这个 Excel 发回即可；不要改动白色格子。</t>
         </is>
       </c>
     </row>
@@ -5692,7 +5771,7 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>漏抽条数（你来填）</t>
+          <t>原文表格中的记录条数（你来数）</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
